--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -37,25 +37,49 @@
     <t xml:space="preserve">KTT Kang White V3 Switches</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005007487740877.html?spm=a2g0o.productlist.main.8.539c2371OWCMK2&amp;aem_p4p_detail=20261024200006669094944086530002248500&amp;algo_pvid=ebf6eb73-3606-426a-83ab-61211c4f6826&amp;algo_exp_id=ebf6eb73-3606-426a-83ab-61211c4f6826-7&amp;pdp_ext_f=%7B%22order%22%3A%22183%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21NPR%21993.75%21617.04%21%21%2143.43%2126.97%21%402141396c17928972060542752e1064%2112000040979340365%21sea%21NP%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A3129fbd1%3Bm03_new_user%3A-29895%3BpisId%3A5000000219357547&amp;curPageLogUid=XOsorIbCjs9y&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005007487740877%7C_p_origin_prod%3A&amp;search_p4p_id=20261024200006669094944086530002248500_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.91 Inch OLED Module</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005006351390199.html?pdp_npi=4%40dis%21NPR%21NPR+169.32%21NPR+165.50%21%21%217.40%217.23%21%402101528c17929044198227411e0dca%2112000036858011577%21sh%21NP%210%21X&amp;spm=a2g0o.store_pc_allItems_or_groupList.new_all_items_2007540639121.1005006351390199</t>
+  </si>
+  <si>
     <t xml:space="preserve">Raspberry Pi Pico Board</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005006071676557.html?spm=a2g0o.productlist.main.8.45cb5f4duNV1mI&amp;aem_p4p_detail=2026102420174910277338441804160002258483&amp;algo_pvid=d1b1276b-5f6e-4c94-961f-805c18ca15b5&amp;algo_exp_id=d1b1276b-5f6e-4c94-961f-805c18ca15b5-7&amp;pdp_ext_f=%7B%22order%22%3A%22741%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21NPR%21251.70%21165.50%21%21%2111.00%217.23%21%40210178d717928982695147439e0c3b%2112000035596473665%21sea%21NP%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A3129fbd1%3Bm03_new_user%3A-29895%3BpisId%3A5000000219357547&amp;curPageLogUid=wN1pDZZKpGob&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005006071676557%7C_p_origin_prod%3A&amp;search_p4p_id=2026102420174910277338441804160002258483_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Taiwan EC11 encoder</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005010569981959.html?spm=a2g0o.productlist.main.1.44af1e84l3x1Rr&amp;algo_pvid=c1d3c5fe-2be0-474a-98e3-ed7d8fb79a93&amp;algo_exp_id=c1d3c5fe-2be0-474a-98e3-ed7d8fb79a93-0&amp;pdp_ext_f=%7B%22order%22%3A%221346%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21NPR%21191.31%21153.35%21%21%211.26%211.01%21%402101364a17928987734711958e0e7c%2112000052851631827%21sea%21NP%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A3129fbd1%3Bm03_new_user%3A-29895&amp;curPageLogUid=9Wfy0rwm94lA&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005010569981959%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
     <t xml:space="preserve">Knurled Brass Insert Nuts</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005008828152264.html?spm=a2g0o.productlist.main.4.77bd5c13qGCMha&amp;aem_p4p_detail=202610242032358916438443914800002328539&amp;algo_pvid=7e810a71-f751-41ea-a0c3-e0a7f5963c91&amp;algo_exp_id=7e810a71-f751-41ea-a0c3-e0a7f5963c91-3&amp;pdp_ext_f=%7B%22order%22%3A%22277%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21NPR%21442.67%21332.00%21%21%2119.35%2114.51%21%402141397017928991553284208e0f19%2112000046848094216%21sea%21NP%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A3129fbd1%3Bm03_new_user%3A-29895&amp;curPageLogUid=2xuoRaaUcolp&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005008828152264%7C_p_origin_prod%3A&amp;search_p4p_id=202610242032358916438443914800002328539_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Push Button</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005008916867707.html?spm=a2g0o.productlist.main.3.5d8e2444BWnrPj&amp;algo_pvid=af675630-5e86-4007-8ec7-3795e574aee0&amp;algo_exp_id=af675630-5e86-4007-8ec7-3795e574aee0-2&amp;pdp_ext_f=%7B%22order%22%3A%2221%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21NPR%2160.73%2160.73%21%21%210.40%210.40%21%400be71e1e17929025011846171e0c82%2112000047195821035%21sea%21NP%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A3129fbd1%3Bm03_new_user%3A-29895&amp;curPageLogUid=QdG27zxey7Lp&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005008916867707%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
     <t xml:space="preserve">Stabilizers </t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005001831944910.html?spm=a2g0o.productlist.main.7.666c624aGZgBxV&amp;algo_pvid=c057f276-c510-45b4-afcb-51ebf7615056&amp;algo_exp_id=c057f276-c510-45b4-afcb-51ebf7615056-6&amp;pdp_ext_f=%7B%22order%22%3A%2248%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21NPR%21809.29%21501.07%21%21%215.33%213.30%21%402141147417929026323494252e0d79%2112000017788498378%21sea%21NP%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A3129fbd1%3Bm03_new_user%3A-29895%3BpisId%3A5000000219357547&amp;curPageLogUid=lA7zUQ0O4afU&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005001831944910%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
     <t xml:space="preserve">PCB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">jlcpcb.com</t>
   </si>
   <si>
     <t xml:space="preserve">3D priting the case </t>
@@ -80,6 +104,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -100,6 +125,7 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -144,20 +170,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -287,123 +317,147 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="29.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="45.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="29.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="45.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>15.35</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="3" t="n">
         <v>15.35</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="n">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="3" t="n">
         <v>2.7</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="n">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>2.26</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="3" t="n">
         <v>3.85</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="n">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="3" t="n">
         <v>1.01</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2" t="n">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="n">
         <v>1.37</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>2.01</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="2" t="n">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>1.15</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="2" t="n">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="3" t="n">
         <v>5.34</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="3" t="n">
         <v>5.34</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="3" t="n">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="4" t="n">
         <v>30.2</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="3" t="n">
         <v>61.4</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>14</v>
+      <c r="A10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t xml:space="preserve">N\A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diodes SOD123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aliexpress.com/item/1005003750245235.html?spm=a2g0o.productlist.main.2.10b543ealUrZe0&amp;algo_pvid=1df4167b-3bb5-4324-9d9d-c272c52bf127&amp;algo_exp_id=1df4167b-3bb5-4324-9d9d-c272c52bf127-1&amp;pdp_ext_f=%7B%22order%22%3A%2240%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21NPR%21148.80%21148.80%21%21%210.98%210.98%21%40212e37eb17929163558418253e0f46%2112000027034650971%21sea%21NP%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A3129fbd1%3Bm03_new_user%3A-29895&amp;curPageLogUid=fxt1HF50DhOq&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005003750245235%7C_p_origin_prod%3A</t>
   </si>
 </sst>
 </file>
@@ -99,7 +105,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="[$$-409]#,##0.00;[RED]\-[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -127,6 +133,13 @@
       <family val="1"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -170,7 +183,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -188,6 +201,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -314,7 +335,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.54"/>
@@ -460,7 +481,24 @@
         <v>22</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D11" r:id="rId1" display="https://www.aliexpress.com/item/1005003750245235.html?spm=a2g0o.productlist.main.2.10b543ealUrZe0&amp;algo_pvid=1df4167b-3bb5-4324-9d9d-c272c52bf127&amp;algo_exp_id=1df4167b-3bb5-4324-9d9d-c272c52bf127-1&amp;pdp_ext_f=%7B%22order%22%3A%2240%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21NPR%21148.80%21148.80%21%21%210.98%210.98%21%40212e37eb17929163558418253e0f46%2112000027034650971%21sea%21NP%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A3129fbd1%3Bm03_new_user%3A-29895&amp;curPageLogUid=fxt1HF50DhOq&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005003750245235%7C_p_origin_prod%3A"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
